--- a/dados_auxiliares/procv_acoes.xlsx
+++ b/dados_auxiliares/procv_acoes.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x526325\OneDrive - rede.sp\painel orçamentário\python\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2D934F-9548-4BE8-9C4C-EF27910A4B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -549,9 +543,6 @@
     <t>Conselho Tutelar</t>
   </si>
   <si>
-    <t>tipo_coordenacao</t>
-  </si>
-  <si>
     <t>Imigrantes</t>
   </si>
   <si>
@@ -604,13 +595,16 @@
   </si>
   <si>
     <t>Conselho</t>
+  </si>
+  <si>
+    <t>acao_programatica</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,27 +686,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B713930F-79CF-43D5-B86F-037DFF2D6545}" name="procv" displayName="procv" ref="A1:D43" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:D43" xr:uid="{B713930F-79CF-43D5-B86F-037DFF2D6545}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="procv" displayName="procv" ref="A1:D43" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:D43"/>
+  <sortState ref="A2:B43">
     <sortCondition ref="A1:A43"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{EBB1A477-110A-4C9D-9320-8CF9F5AA58EC}" name="acao" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{F9655FA5-0D00-4739-B24B-69F711637B64}" name="coordenadoria" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{04C59391-15F0-437F-A41E-FE509A61B6B8}" name="tipo_coordenacao" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{EB60E2AF-7FE1-479C-A98E-2330793915E1}" name="politicas_para" dataDxfId="4"/>
+    <tableColumn id="1" name="acao" dataDxfId="7"/>
+    <tableColumn id="2" name="coordenadoria" dataDxfId="6"/>
+    <tableColumn id="3" name="acao_programatica" dataDxfId="5"/>
+    <tableColumn id="4" name="politicas_para" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63EFC552-63A9-4585-871C-22535C6E230B}" name="Tabela1" displayName="Tabela1" ref="F1:G81" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="F1:G81" xr:uid="{63EFC552-63A9-4585-871C-22535C6E230B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="F1:G81" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="F1:G81"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8D3EEA23-6FF3-425B-8C4F-0884C3C9131B}" name="ProjetoAtividade" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{0E9955FE-47F7-4826-9C9F-44C4DAFA1B9B}" name="Ds_Projeto_Atividade" dataDxfId="0"/>
+    <tableColumn id="1" name="ProjetoAtividade" dataDxfId="1"/>
+    <tableColumn id="2" name="Ds_Projeto_Atividade" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -761,7 +755,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -813,7 +807,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1027,29 +1021,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC618BA-A711-4796-8900-8DC318D21694}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="85.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.375" customWidth="1"/>
+    <col min="6" max="6" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="85.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -1057,7 +1051,7 @@
         <v>171</v>
       </c>
       <c r="C1" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
         <v>172</v>
@@ -1069,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1089,7 +1083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1109,7 +1103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1120,7 +1114,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F4">
         <v>2051</v>
@@ -1129,7 +1123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -1140,7 +1134,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F5">
         <v>2053</v>
@@ -1149,7 +1143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1160,7 +1154,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F6">
         <v>2100</v>
@@ -1169,7 +1163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,7 +1174,7 @@
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F7">
         <v>2106</v>
@@ -1189,7 +1183,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1200,7 +1194,7 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F8">
         <v>2142</v>
@@ -1209,7 +1203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -1229,7 +1223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -1249,7 +1243,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -1260,7 +1254,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11">
         <v>2180</v>
@@ -1269,7 +1263,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1280,7 +1274,7 @@
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F12">
         <v>2431</v>
@@ -1289,18 +1283,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F13">
         <v>2818</v>
@@ -1309,7 +1303,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -1320,7 +1314,7 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F14">
         <v>3002</v>
@@ -1329,7 +1323,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
@@ -1349,7 +1343,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -1360,7 +1354,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F16">
         <v>3660</v>
@@ -1369,7 +1363,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -1389,7 +1383,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>53</v>
       </c>
@@ -1409,7 +1403,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
@@ -1420,7 +1414,7 @@
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F19">
         <v>4318</v>
@@ -1429,7 +1423,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -1440,7 +1434,7 @@
         <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F20">
         <v>4319</v>
@@ -1449,7 +1443,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>61</v>
       </c>
@@ -1460,7 +1454,7 @@
         <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F21">
         <v>4320</v>
@@ -1469,7 +1463,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>64</v>
       </c>
@@ -1480,7 +1474,7 @@
         <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F22">
         <v>4321</v>
@@ -1489,7 +1483,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>67</v>
       </c>
@@ -1500,7 +1494,7 @@
         <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F23">
         <v>4322</v>
@@ -1509,7 +1503,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>71</v>
       </c>
@@ -1520,7 +1514,7 @@
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F24">
         <v>4324</v>
@@ -1529,7 +1523,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
         <v>75</v>
       </c>
@@ -1540,7 +1534,7 @@
         <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F25">
         <v>4325</v>
@@ -1549,7 +1543,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
         <v>78</v>
       </c>
@@ -1560,7 +1554,7 @@
         <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F26">
         <v>4326</v>
@@ -1569,7 +1563,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
         <v>81</v>
       </c>
@@ -1580,7 +1574,7 @@
         <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F27">
         <v>4327</v>
@@ -1589,7 +1583,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
         <v>84</v>
       </c>
@@ -1600,7 +1594,7 @@
         <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F28">
         <v>4328</v>
@@ -1609,7 +1603,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>87</v>
       </c>
@@ -1620,7 +1614,7 @@
         <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F29">
         <v>4329</v>
@@ -1629,7 +1623,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
         <v>90</v>
       </c>
@@ -1640,7 +1634,7 @@
         <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F30">
         <v>4330</v>
@@ -1649,7 +1643,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
         <v>94</v>
       </c>
@@ -1660,7 +1654,7 @@
         <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F31">
         <v>4332</v>
@@ -1669,7 +1663,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
@@ -1680,7 +1674,7 @@
         <v>98</v>
       </c>
       <c r="D32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F32">
         <v>4333</v>
@@ -1689,7 +1683,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
         <v>100</v>
       </c>
@@ -1700,7 +1694,7 @@
         <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F33">
         <v>4334</v>
@@ -1709,7 +1703,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
         <v>103</v>
       </c>
@@ -1720,7 +1714,7 @@
         <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F34">
         <v>4335</v>
@@ -1729,7 +1723,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
         <v>106</v>
       </c>
@@ -1740,7 +1734,7 @@
         <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F35">
         <v>4422</v>
@@ -1749,7 +1743,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
         <v>109</v>
       </c>
@@ -1760,7 +1754,7 @@
         <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F36">
         <v>4426</v>
@@ -1769,7 +1763,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
         <v>112</v>
       </c>
@@ -1789,7 +1783,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
         <v>115</v>
       </c>
@@ -1800,7 +1794,7 @@
         <v>116</v>
       </c>
       <c r="D38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F38">
         <v>4820</v>
@@ -1809,7 +1803,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
         <v>118</v>
       </c>
@@ -1820,7 +1814,7 @@
         <v>119</v>
       </c>
       <c r="D39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F39">
         <v>5474</v>
@@ -1829,7 +1823,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
         <v>121</v>
       </c>
@@ -1849,7 +1843,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
         <v>124</v>
       </c>
@@ -1860,7 +1854,7 @@
         <v>125</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F41">
         <v>7001</v>
@@ -1869,7 +1863,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
         <v>127</v>
       </c>
@@ -1880,7 +1874,7 @@
         <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F42">
         <v>8006</v>
@@ -1889,7 +1883,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
         <v>130</v>
       </c>
@@ -1900,7 +1894,7 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F43">
         <v>8064</v>
@@ -1909,7 +1903,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="F44">
         <v>8065</v>
       </c>
@@ -1917,7 +1911,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="F45">
         <v>8081</v>
       </c>
@@ -1925,7 +1919,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="F46">
         <v>8082</v>
       </c>
@@ -1933,7 +1927,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="F47">
         <v>9006</v>
       </c>
@@ -1941,7 +1935,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="F48">
         <v>9065</v>
       </c>
@@ -1949,7 +1943,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:7">
       <c r="F49">
         <v>9074</v>
       </c>
@@ -1957,7 +1951,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:7">
       <c r="F50">
         <v>9078</v>
       </c>
@@ -1965,7 +1959,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:7">
       <c r="F51">
         <v>9079</v>
       </c>
@@ -1973,7 +1967,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:7">
       <c r="F52">
         <v>9080</v>
       </c>
@@ -1981,7 +1975,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:7">
       <c r="F53">
         <v>9089</v>
       </c>
@@ -1989,7 +1983,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:7">
       <c r="F54">
         <v>9090</v>
       </c>
@@ -1997,7 +1991,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:7">
       <c r="F55">
         <v>9109</v>
       </c>
@@ -2005,7 +1999,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="56" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:7">
       <c r="F56">
         <v>9124</v>
       </c>
@@ -2013,7 +2007,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="57" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:7">
       <c r="F57">
         <v>9127</v>
       </c>
@@ -2021,7 +2015,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="58" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:7">
       <c r="F58">
         <v>9139</v>
       </c>
@@ -2029,7 +2023,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:7">
       <c r="F59">
         <v>9146</v>
       </c>
@@ -2037,7 +2031,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="60" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:7">
       <c r="F60">
         <v>9193</v>
       </c>
@@ -2045,7 +2039,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:7">
       <c r="F61">
         <v>9196</v>
       </c>
@@ -2053,7 +2047,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:7">
       <c r="F62">
         <v>9198</v>
       </c>
@@ -2061,7 +2055,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:7">
       <c r="F63">
         <v>9199</v>
       </c>
@@ -2069,7 +2063,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:7">
       <c r="F64">
         <v>9201</v>
       </c>
@@ -2077,7 +2071,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="65" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:7">
       <c r="F65">
         <v>9205</v>
       </c>
@@ -2085,7 +2079,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="66" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:7">
       <c r="F66">
         <v>9208</v>
       </c>
@@ -2093,7 +2087,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:7">
       <c r="F67">
         <v>9228</v>
       </c>
@@ -2101,7 +2095,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="68" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:7">
       <c r="F68">
         <v>9229</v>
       </c>
@@ -2109,7 +2103,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="69" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:7">
       <c r="F69">
         <v>9230</v>
       </c>
@@ -2117,7 +2111,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="70" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:7">
       <c r="F70">
         <v>9231</v>
       </c>
@@ -2125,7 +2119,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:7">
       <c r="F71">
         <v>9232</v>
       </c>
@@ -2133,7 +2127,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="72" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:7">
       <c r="F72">
         <v>9234</v>
       </c>
@@ -2141,7 +2135,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="73" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:7">
       <c r="F73">
         <v>9235</v>
       </c>
@@ -2149,7 +2143,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="74" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:7">
       <c r="F74">
         <v>9237</v>
       </c>
@@ -2157,7 +2151,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="75" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:7">
       <c r="F75">
         <v>9240</v>
       </c>
@@ -2165,7 +2159,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="76" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:7">
       <c r="F76">
         <v>9241</v>
       </c>
@@ -2173,7 +2167,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:7">
       <c r="F77">
         <v>9242</v>
       </c>
@@ -2181,7 +2175,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:7">
       <c r="F78">
         <v>9243</v>
       </c>
@@ -2189,7 +2183,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="79" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:7">
       <c r="F79">
         <v>9244</v>
       </c>
@@ -2197,7 +2191,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="80" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:7">
       <c r="F80">
         <v>9251</v>
       </c>
@@ -2205,7 +2199,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="6:7">
       <c r="F81">
         <v>9253</v>
       </c>

--- a/dados_auxiliares/procv_acoes.xlsx
+++ b/dados_auxiliares/procv_acoes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="205">
   <si>
     <t>ProjetoAtividade</t>
   </si>
@@ -153,9 +153,6 @@
     <t>2818</t>
   </si>
   <si>
-    <t>Tecnologia - Comunicação</t>
-  </si>
-  <si>
     <t>Implementação do Selo Municipal de Direitos Humanos e Diversidade</t>
   </si>
   <si>
@@ -198,9 +195,6 @@
     <t>4314</t>
   </si>
   <si>
-    <t>Desaparecidas</t>
-  </si>
-  <si>
     <t>Políticas, Programas e Ações Inclusivas</t>
   </si>
   <si>
@@ -360,27 +354,18 @@
     <t>4335</t>
   </si>
   <si>
-    <t>Egressos</t>
-  </si>
-  <si>
     <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
   </si>
   <si>
     <t>4426</t>
   </si>
   <si>
-    <t>Sesana - Políticas</t>
-  </si>
-  <si>
     <t>Manutenção, Programas e Suporte da Coordenadoria de Defesa do Consumidor</t>
   </si>
   <si>
     <t>4470</t>
   </si>
   <si>
-    <t>Sesana - Cresan</t>
-  </si>
-  <si>
     <t>Ampliação, Reforma e Requalificação de Centro de Referência de Segurança Alimentar e Nutricional</t>
   </si>
   <si>
@@ -570,9 +555,6 @@
     <t>Desaparecidos</t>
   </si>
   <si>
-    <t>Memória e Verdade</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -598,6 +580,60 @@
   </si>
   <si>
     <t>acao_programatica</t>
+  </si>
+  <si>
+    <t>DTIC</t>
+  </si>
+  <si>
+    <t>DTIC - Desenvolvimento</t>
+  </si>
+  <si>
+    <t>DTIC - Manutenção</t>
+  </si>
+  <si>
+    <t>DTIC - Comunicação</t>
+  </si>
+  <si>
+    <t>Selo Direitos Humanos</t>
+  </si>
+  <si>
+    <t>CLFD</t>
+  </si>
+  <si>
+    <t>CLFD - Políticas</t>
+  </si>
+  <si>
+    <t>Direito à Memória e Verdade</t>
+  </si>
+  <si>
+    <t>CPJ - Políticas</t>
+  </si>
+  <si>
+    <t>COPIND - Políticas</t>
+  </si>
+  <si>
+    <t>CPD - Políticas</t>
+  </si>
+  <si>
+    <t>CPCA - Políticas</t>
+  </si>
+  <si>
+    <t>ODH - Manutenção</t>
+  </si>
+  <si>
+    <t>CPEF</t>
+  </si>
+  <si>
+    <t>CPEF - Políticas</t>
+  </si>
+  <si>
+    <t>Egressos e Familiares</t>
+  </si>
+  <si>
+    <t>SESANA - Políticas</t>
+  </si>
+  <si>
+    <t>SESANA - CRESAN</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1057,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1043,18 +1079,18 @@
     <col min="7" max="7" width="85.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -1068,10 +1104,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1094,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F3">
         <v>2033</v>
@@ -1114,7 +1150,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F4">
         <v>2051</v>
@@ -1134,7 +1170,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F5">
         <v>2053</v>
@@ -1154,7 +1190,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F6">
         <v>2100</v>
@@ -1174,7 +1210,7 @@
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F7">
         <v>2106</v>
@@ -1194,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F8">
         <v>2142</v>
@@ -1214,7 +1250,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F9">
         <v>2157</v>
@@ -1228,10 +1264,10 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -1254,7 +1290,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F11">
         <v>2180</v>
@@ -1274,7 +1310,7 @@
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F12">
         <v>2431</v>
@@ -1288,13 +1324,13 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F13">
         <v>2818</v>
@@ -1314,7 +1350,7 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F14">
         <v>3002</v>
@@ -1328,10 +1364,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -1340,567 +1376,567 @@
         <v>3406</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
       <c r="D16" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F16">
         <v>3660</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
         <v>50</v>
       </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="F17">
         <v>4314</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18">
         <v>4317</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F19">
         <v>4318</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F20">
         <v>4319</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F21">
         <v>4320</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="D22" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F22">
         <v>4321</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
         <v>67</v>
       </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
-      </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F23">
         <v>4322</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
         <v>71</v>
       </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
       <c r="D24" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F24">
         <v>4324</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F25">
         <v>4325</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F26">
         <v>4326</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F27">
         <v>4327</v>
       </c>
       <c r="G27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F28">
         <v>4328</v>
       </c>
       <c r="G28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F29">
         <v>4329</v>
       </c>
       <c r="G29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" t="s">
         <v>90</v>
       </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
       <c r="D30" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F30">
         <v>4330</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F31">
         <v>4332</v>
       </c>
       <c r="G31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F32">
         <v>4333</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F33">
         <v>4334</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="D34" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F34">
         <v>4335</v>
       </c>
       <c r="G34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F35">
         <v>4422</v>
       </c>
       <c r="G35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F36">
         <v>4426</v>
       </c>
       <c r="G36" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="D37" t="s">
-        <v>113</v>
+        <v>202</v>
       </c>
       <c r="F37">
         <v>4470</v>
       </c>
       <c r="G37" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F38">
         <v>4820</v>
       </c>
       <c r="G38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F39">
         <v>5474</v>
       </c>
       <c r="G39" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B40" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F40">
         <v>6178</v>
       </c>
       <c r="G40" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F41">
         <v>7001</v>
       </c>
       <c r="G41" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D42" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F42">
         <v>8006</v>
       </c>
       <c r="G42" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" t="s">
         <v>47</v>
       </c>
-      <c r="C43" t="s">
-        <v>48</v>
-      </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F43">
         <v>8064</v>
       </c>
       <c r="G43" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1908,7 +1944,7 @@
         <v>8065</v>
       </c>
       <c r="G44" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1916,7 +1952,7 @@
         <v>8081</v>
       </c>
       <c r="G45" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1924,7 +1960,7 @@
         <v>8082</v>
       </c>
       <c r="G46" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1932,7 +1968,7 @@
         <v>9006</v>
       </c>
       <c r="G47" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1940,7 +1976,7 @@
         <v>9065</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="6:7">
@@ -1948,7 +1984,7 @@
         <v>9074</v>
       </c>
       <c r="G49" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="6:7">
@@ -1956,7 +1992,7 @@
         <v>9078</v>
       </c>
       <c r="G50" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="6:7">
@@ -1964,7 +2000,7 @@
         <v>9079</v>
       </c>
       <c r="G51" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="6:7">
@@ -1972,7 +2008,7 @@
         <v>9080</v>
       </c>
       <c r="G52" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="6:7">
@@ -1980,7 +2016,7 @@
         <v>9089</v>
       </c>
       <c r="G53" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="6:7">
@@ -1988,7 +2024,7 @@
         <v>9090</v>
       </c>
       <c r="G54" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="6:7">
@@ -1996,7 +2032,7 @@
         <v>9109</v>
       </c>
       <c r="G55" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="56" spans="6:7">
@@ -2004,7 +2040,7 @@
         <v>9124</v>
       </c>
       <c r="G56" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="6:7">
@@ -2012,7 +2048,7 @@
         <v>9127</v>
       </c>
       <c r="G57" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="6:7">
@@ -2020,7 +2056,7 @@
         <v>9139</v>
       </c>
       <c r="G58" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="6:7">
@@ -2028,7 +2064,7 @@
         <v>9146</v>
       </c>
       <c r="G59" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="6:7">
@@ -2036,7 +2072,7 @@
         <v>9193</v>
       </c>
       <c r="G60" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61" spans="6:7">
@@ -2044,7 +2080,7 @@
         <v>9196</v>
       </c>
       <c r="G61" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="6:7">
@@ -2052,7 +2088,7 @@
         <v>9198</v>
       </c>
       <c r="G62" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="6:7">
@@ -2060,7 +2096,7 @@
         <v>9199</v>
       </c>
       <c r="G63" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="6:7">
@@ -2068,7 +2104,7 @@
         <v>9201</v>
       </c>
       <c r="G64" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="6:7">
@@ -2076,7 +2112,7 @@
         <v>9205</v>
       </c>
       <c r="G65" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="6:7">
@@ -2084,7 +2120,7 @@
         <v>9208</v>
       </c>
       <c r="G66" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="6:7">
@@ -2092,7 +2128,7 @@
         <v>9228</v>
       </c>
       <c r="G67" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="6:7">
@@ -2100,7 +2136,7 @@
         <v>9229</v>
       </c>
       <c r="G68" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="6:7">
@@ -2108,7 +2144,7 @@
         <v>9230</v>
       </c>
       <c r="G69" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="6:7">
@@ -2116,7 +2152,7 @@
         <v>9231</v>
       </c>
       <c r="G70" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="6:7">
@@ -2124,7 +2160,7 @@
         <v>9232</v>
       </c>
       <c r="G71" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="6:7">
@@ -2132,7 +2168,7 @@
         <v>9234</v>
       </c>
       <c r="G72" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="6:7">
@@ -2140,7 +2176,7 @@
         <v>9235</v>
       </c>
       <c r="G73" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="6:7">
@@ -2148,7 +2184,7 @@
         <v>9237</v>
       </c>
       <c r="G74" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="6:7">
@@ -2156,7 +2192,7 @@
         <v>9240</v>
       </c>
       <c r="G75" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="6:7">
@@ -2164,7 +2200,7 @@
         <v>9241</v>
       </c>
       <c r="G76" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="6:7">
@@ -2172,7 +2208,7 @@
         <v>9242</v>
       </c>
       <c r="G77" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" spans="6:7">
@@ -2180,7 +2216,7 @@
         <v>9243</v>
       </c>
       <c r="G78" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="6:7">
@@ -2188,7 +2224,7 @@
         <v>9244</v>
       </c>
       <c r="G79" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="80" spans="6:7">
@@ -2196,7 +2232,7 @@
         <v>9251</v>
       </c>
       <c r="G80" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="6:7">
@@ -2204,7 +2240,7 @@
         <v>9253</v>
       </c>
       <c r="G81" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/dados_auxiliares/procv_acoes.xlsx
+++ b/dados_auxiliares/procv_acoes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="206">
   <si>
     <t>ProjetoAtividade</t>
   </si>
@@ -66,9 +66,6 @@
     <t>CPM</t>
   </si>
   <si>
-    <t>CPM - CMB</t>
-  </si>
-  <si>
     <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
   </si>
   <si>
@@ -634,6 +631,12 @@
   </si>
   <si>
     <t>SESANA - CRESAN</t>
+  </si>
+  <si>
+    <t>Planejamento e Informação</t>
+  </si>
+  <si>
+    <t>CPM - Casa da Mulher Brasileira</t>
   </si>
 </sst>
 </file>
@@ -669,9 +672,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1081,16 +1085,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" t="s">
         <v>166</v>
-      </c>
-      <c r="C1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D1" t="s">
-        <v>167</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -1104,10 +1108,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
         <v>187</v>
-      </c>
-      <c r="C2" t="s">
-        <v>188</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1130,7 +1134,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>2033</v>
@@ -1150,7 +1154,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F4">
         <v>2051</v>
@@ -1167,107 +1171,107 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F5">
         <v>2053</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6">
         <v>2100</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F7">
         <v>2106</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8">
         <v>2142</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F9">
         <v>2157</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -1276,98 +1280,98 @@
         <v>2171</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="F11">
         <v>2180</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>173</v>
+      <c r="D12" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F12">
         <v>2431</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F13">
         <v>2818</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F14">
         <v>3002</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -1376,567 +1380,567 @@
         <v>3406</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F16">
         <v>3660</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
         <v>49</v>
       </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F17">
         <v>4314</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18">
         <v>4317</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
         <v>54</v>
       </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F19">
         <v>4318</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" t="s">
         <v>192</v>
       </c>
-      <c r="C20" t="s">
-        <v>193</v>
-      </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F20">
         <v>4319</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
         <v>59</v>
       </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F21">
         <v>4320</v>
       </c>
       <c r="G21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
         <v>62</v>
       </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F22">
         <v>4321</v>
       </c>
       <c r="G22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
         <v>65</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>66</v>
       </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
       <c r="D23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F23">
         <v>4322</v>
       </c>
       <c r="G23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
         <v>69</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>70</v>
       </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F24">
         <v>4324</v>
       </c>
       <c r="G24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F25">
         <v>4325</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
         <v>76</v>
       </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F26">
         <v>4326</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F27">
         <v>4327</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F28">
         <v>4328</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
         <v>85</v>
       </c>
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F29">
         <v>4329</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>89</v>
       </c>
-      <c r="C30" t="s">
-        <v>90</v>
-      </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F30">
         <v>4330</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
         <v>92</v>
       </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F31">
         <v>4332</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F32">
         <v>4333</v>
       </c>
       <c r="G32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" t="s">
         <v>98</v>
       </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F33">
         <v>4334</v>
       </c>
       <c r="G33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
         <v>101</v>
       </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
       <c r="C34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F34">
         <v>4335</v>
       </c>
       <c r="G34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
         <v>104</v>
       </c>
-      <c r="B35" t="s">
-        <v>105</v>
-      </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F35">
         <v>4422</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
         <v>107</v>
       </c>
-      <c r="B36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" t="s">
-        <v>108</v>
-      </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F36">
         <v>4426</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" t="s">
         <v>200</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>201</v>
-      </c>
-      <c r="D37" t="s">
-        <v>202</v>
       </c>
       <c r="F37">
         <v>4470</v>
       </c>
       <c r="G37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F38">
         <v>4820</v>
       </c>
       <c r="G38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F39">
         <v>5474</v>
       </c>
       <c r="G39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
         <v>116</v>
       </c>
-      <c r="B40" t="s">
-        <v>117</v>
-      </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F40">
         <v>6178</v>
       </c>
       <c r="G40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" t="s">
         <v>119</v>
       </c>
-      <c r="B41" t="s">
-        <v>120</v>
-      </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F41">
         <v>7001</v>
       </c>
       <c r="G41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F42">
         <v>8006</v>
       </c>
       <c r="G42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" t="s">
         <v>46</v>
       </c>
-      <c r="C43" t="s">
-        <v>47</v>
-      </c>
       <c r="D43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F43">
         <v>8064</v>
       </c>
       <c r="G43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1944,7 +1948,7 @@
         <v>8065</v>
       </c>
       <c r="G44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1952,7 +1956,7 @@
         <v>8081</v>
       </c>
       <c r="G45" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1960,7 +1964,7 @@
         <v>8082</v>
       </c>
       <c r="G46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1968,7 +1972,7 @@
         <v>9006</v>
       </c>
       <c r="G47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1976,7 +1980,7 @@
         <v>9065</v>
       </c>
       <c r="G48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="6:7">
@@ -1984,7 +1988,7 @@
         <v>9074</v>
       </c>
       <c r="G49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="6:7">
@@ -1992,7 +1996,7 @@
         <v>9078</v>
       </c>
       <c r="G50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="6:7">
@@ -2000,7 +2004,7 @@
         <v>9079</v>
       </c>
       <c r="G51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="6:7">
@@ -2008,7 +2012,7 @@
         <v>9080</v>
       </c>
       <c r="G52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="6:7">
@@ -2016,7 +2020,7 @@
         <v>9089</v>
       </c>
       <c r="G53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="6:7">
@@ -2024,7 +2028,7 @@
         <v>9090</v>
       </c>
       <c r="G54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="6:7">
@@ -2032,7 +2036,7 @@
         <v>9109</v>
       </c>
       <c r="G55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="6:7">
@@ -2040,7 +2044,7 @@
         <v>9124</v>
       </c>
       <c r="G56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="6:7">
@@ -2048,7 +2052,7 @@
         <v>9127</v>
       </c>
       <c r="G57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="6:7">
@@ -2056,7 +2060,7 @@
         <v>9139</v>
       </c>
       <c r="G58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="6:7">
@@ -2064,7 +2068,7 @@
         <v>9146</v>
       </c>
       <c r="G59" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="6:7">
@@ -2072,7 +2076,7 @@
         <v>9193</v>
       </c>
       <c r="G60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="6:7">
@@ -2080,7 +2084,7 @@
         <v>9196</v>
       </c>
       <c r="G61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="6:7">
@@ -2088,7 +2092,7 @@
         <v>9198</v>
       </c>
       <c r="G62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="6:7">
@@ -2096,7 +2100,7 @@
         <v>9199</v>
       </c>
       <c r="G63" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="6:7">
@@ -2104,7 +2108,7 @@
         <v>9201</v>
       </c>
       <c r="G64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="6:7">
@@ -2112,7 +2116,7 @@
         <v>9205</v>
       </c>
       <c r="G65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="6:7">
@@ -2120,7 +2124,7 @@
         <v>9208</v>
       </c>
       <c r="G66" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="6:7">
@@ -2128,7 +2132,7 @@
         <v>9228</v>
       </c>
       <c r="G67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="6:7">
@@ -2136,7 +2140,7 @@
         <v>9229</v>
       </c>
       <c r="G68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="6:7">
@@ -2144,7 +2148,7 @@
         <v>9230</v>
       </c>
       <c r="G69" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" spans="6:7">
@@ -2152,7 +2156,7 @@
         <v>9231</v>
       </c>
       <c r="G70" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="6:7">
@@ -2160,7 +2164,7 @@
         <v>9232</v>
       </c>
       <c r="G71" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="6:7">
@@ -2168,7 +2172,7 @@
         <v>9234</v>
       </c>
       <c r="G72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="6:7">
@@ -2176,7 +2180,7 @@
         <v>9235</v>
       </c>
       <c r="G73" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="6:7">
@@ -2184,7 +2188,7 @@
         <v>9237</v>
       </c>
       <c r="G74" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="75" spans="6:7">
@@ -2192,7 +2196,7 @@
         <v>9240</v>
       </c>
       <c r="G75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" spans="6:7">
@@ -2200,7 +2204,7 @@
         <v>9241</v>
       </c>
       <c r="G76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="77" spans="6:7">
@@ -2208,7 +2212,7 @@
         <v>9242</v>
       </c>
       <c r="G77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="6:7">
@@ -2216,7 +2220,7 @@
         <v>9243</v>
       </c>
       <c r="G78" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" spans="6:7">
@@ -2224,7 +2228,7 @@
         <v>9244</v>
       </c>
       <c r="G79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="6:7">
@@ -2232,7 +2236,7 @@
         <v>9251</v>
       </c>
       <c r="G80" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="81" spans="6:7">
@@ -2240,16 +2244,16 @@
         <v>9253</v>
       </c>
       <c r="G81" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>